--- a/data/routes_corretgides.xlsx
+++ b/data/routes_corretgides.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jordiordonezadellach/Desktop/rando/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/33c026b07bb50802/Feina/DataApps^0Learning/rando/andorra-skimo-bulletin/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DA7092-20EF-3849-ACEC-7806277071BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{91DA7092-20EF-3849-ACEC-7806277071BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDBF4CF9-95B0-4743-BC36-2FD7AC385F91}"/>
   <bookViews>
     <workbookView xWindow="17540" yWindow="7660" windowWidth="40380" windowHeight="17440" xr2:uid="{DACA9C36-F0F5-EC4B-9BA5-459550E34FB7}"/>
   </bookViews>
@@ -299,9 +299,6 @@
     <t>Pàrquing de Sorteny, a 1780m</t>
   </si>
   <si>
-    <t>Cap de la Tosa d'</t>
-  </si>
-  <si>
     <t>2.5km</t>
   </si>
   <si>
@@ -1665,6 +1662,9 @@
   </si>
   <si>
     <t>N+NE+W</t>
+  </si>
+  <si>
+    <t>Cap de la Tosa d'Entor</t>
   </si>
 </sst>
 </file>
@@ -2165,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -2174,7 +2174,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -2269,7 +2269,7 @@
         <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="J3" t="s">
         <v>22</v>
@@ -2312,7 +2312,7 @@
         <v>27</v>
       </c>
       <c r="I4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J4" t="s">
         <v>28</v>
@@ -2441,7 +2441,7 @@
         <v>48</v>
       </c>
       <c r="I7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J7" t="s">
         <v>49</v>
@@ -2699,7 +2699,7 @@
         <v>81</v>
       </c>
       <c r="I13" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J13" t="s">
         <v>82</v>
@@ -2719,7 +2719,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>538</v>
       </c>
       <c r="C14" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -2736,19 +2736,19 @@
         <v>SIMPLE</v>
       </c>
       <c r="G14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" t="s">
         <v>84</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>85</v>
-      </c>
-      <c r="I14" t="s">
-        <v>86</v>
       </c>
       <c r="J14" t="s">
         <v>43</v>
       </c>
       <c r="K14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L14">
         <v>1940</v>
@@ -2762,7 +2762,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C15" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -2779,19 +2779,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" t="s">
         <v>89</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
+        <v>505</v>
+      </c>
+      <c r="J15" t="s">
         <v>90</v>
       </c>
-      <c r="I15" t="s">
-        <v>506</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>91</v>
-      </c>
-      <c r="K15" t="s">
-        <v>92</v>
       </c>
       <c r="L15">
         <v>1618</v>
@@ -2805,7 +2805,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -2825,16 +2825,16 @@
         <v>58</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I16" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="J16" t="s">
         <v>49</v>
       </c>
       <c r="K16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L16">
         <v>2100</v>
@@ -2848,7 +2848,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -2865,19 +2865,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" t="s">
         <v>97</v>
       </c>
-      <c r="H17" t="s">
-        <v>98</v>
-      </c>
       <c r="I17" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="J17" t="s">
         <v>49</v>
       </c>
       <c r="K17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L17">
         <v>2100</v>
@@ -2891,14 +2891,14 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" t="str">
+        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
+        <v>zona_nord</v>
+      </c>
+      <c r="D18" t="s">
         <v>100</v>
-      </c>
-      <c r="C18" t="str">
-        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
-        <v>zona_nord</v>
-      </c>
-      <c r="D18" t="s">
-        <v>101</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
@@ -2908,19 +2908,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H18" t="s">
         <v>102</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>103</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>104</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>105</v>
-      </c>
-      <c r="K18" t="s">
-        <v>106</v>
       </c>
       <c r="L18">
         <v>1940</v>
@@ -2934,14 +2934,14 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C19" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>13</v>
@@ -2951,19 +2951,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G19" t="s">
+        <v>107</v>
+      </c>
+      <c r="H19" t="s">
         <v>108</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>109</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>110</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>111</v>
-      </c>
-      <c r="K19" t="s">
-        <v>112</v>
       </c>
       <c r="L19">
         <v>2090</v>
@@ -2977,7 +2977,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C20" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -2997,16 +2997,16 @@
         <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I20" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J20" t="s">
         <v>49</v>
       </c>
       <c r="K20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L20">
         <v>2100</v>
@@ -3020,7 +3020,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C21" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3037,19 +3037,19 @@
         <v>SIMPLE</v>
       </c>
       <c r="G21" t="s">
+        <v>116</v>
+      </c>
+      <c r="H21" t="s">
         <v>117</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>118</v>
-      </c>
-      <c r="I21" t="s">
-        <v>119</v>
       </c>
       <c r="J21" t="s">
         <v>49</v>
       </c>
       <c r="K21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L21">
         <v>2100</v>
@@ -3063,7 +3063,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C22" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3083,16 +3083,16 @@
         <v>26</v>
       </c>
       <c r="H22" t="s">
+        <v>121</v>
+      </c>
+      <c r="I22" t="s">
         <v>122</v>
-      </c>
-      <c r="I22" t="s">
-        <v>123</v>
       </c>
       <c r="J22" t="s">
         <v>49</v>
       </c>
       <c r="K22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L22">
         <v>2100</v>
@@ -3106,14 +3106,14 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" t="str">
+        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
+        <v>zona_centre</v>
+      </c>
+      <c r="D23" t="s">
         <v>125</v>
-      </c>
-      <c r="C23" t="str">
-        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
-        <v>zona_centre</v>
-      </c>
-      <c r="D23" t="s">
-        <v>126</v>
       </c>
       <c r="E23" t="s">
         <v>25</v>
@@ -3123,19 +3123,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G23" t="s">
+        <v>126</v>
+      </c>
+      <c r="H23" t="s">
         <v>127</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
+        <v>509</v>
+      </c>
+      <c r="J23" t="s">
         <v>128</v>
       </c>
-      <c r="I23" t="s">
-        <v>510</v>
-      </c>
-      <c r="J23" t="s">
-        <v>129</v>
-      </c>
       <c r="K23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L23">
         <v>1232</v>
@@ -3149,14 +3149,14 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" t="str">
+        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
+        <v>zona_nord</v>
+      </c>
+      <c r="D24" t="s">
         <v>130</v>
-      </c>
-      <c r="C24" t="str">
-        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
-        <v>zona_nord</v>
-      </c>
-      <c r="D24" t="s">
-        <v>131</v>
       </c>
       <c r="E24" t="s">
         <v>13</v>
@@ -3166,19 +3166,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G24" t="s">
+        <v>131</v>
+      </c>
+      <c r="H24" t="s">
         <v>132</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
+        <v>504</v>
+      </c>
+      <c r="J24" t="s">
         <v>133</v>
       </c>
-      <c r="I24" t="s">
-        <v>505</v>
-      </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>134</v>
-      </c>
-      <c r="K24" t="s">
-        <v>135</v>
       </c>
       <c r="L24">
         <v>1920</v>
@@ -3192,7 +3192,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C25" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3209,19 +3209,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G25" t="s">
+        <v>136</v>
+      </c>
+      <c r="H25" t="s">
         <v>137</v>
       </c>
-      <c r="H25" t="s">
-        <v>138</v>
-      </c>
       <c r="I25" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J25" t="s">
         <v>28</v>
       </c>
       <c r="K25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L25">
         <v>1887</v>
@@ -3235,7 +3235,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C26" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3255,7 +3255,7 @@
         <v>80</v>
       </c>
       <c r="H26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I26" t="s">
         <v>70</v>
@@ -3264,7 +3264,7 @@
         <v>82</v>
       </c>
       <c r="K26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L26">
         <v>1780</v>
@@ -3278,14 +3278,14 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C27" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D27" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E27" t="s">
         <v>13</v>
@@ -3295,19 +3295,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G27" t="s">
+        <v>143</v>
+      </c>
+      <c r="H27" t="s">
         <v>144</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>145</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>146</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>147</v>
-      </c>
-      <c r="K27" t="s">
-        <v>148</v>
       </c>
       <c r="L27">
         <v>1825</v>
@@ -3321,14 +3321,14 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" t="str">
+        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
+        <v>zona_centre</v>
+      </c>
+      <c r="D28" t="s">
         <v>149</v>
-      </c>
-      <c r="C28" t="str">
-        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
-        <v>zona_centre</v>
-      </c>
-      <c r="D28" t="s">
-        <v>150</v>
       </c>
       <c r="E28" t="s">
         <v>25</v>
@@ -3338,19 +3338,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G28" t="s">
+        <v>150</v>
+      </c>
+      <c r="H28" t="s">
         <v>151</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>152</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>153</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>154</v>
-      </c>
-      <c r="K28" t="s">
-        <v>155</v>
       </c>
       <c r="L28">
         <v>1340</v>
@@ -3364,7 +3364,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C29" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3381,10 +3381,10 @@
         <v>SIMPLE</v>
       </c>
       <c r="G29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H29" t="s">
         <v>157</v>
-      </c>
-      <c r="H29" t="s">
-        <v>158</v>
       </c>
       <c r="I29" t="s">
         <v>34</v>
@@ -3393,7 +3393,7 @@
         <v>35</v>
       </c>
       <c r="K29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L29">
         <v>1720</v>
@@ -3407,7 +3407,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C30" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3424,19 +3424,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G30" t="s">
+        <v>160</v>
+      </c>
+      <c r="H30" t="s">
         <v>161</v>
       </c>
-      <c r="H30" t="s">
-        <v>162</v>
-      </c>
       <c r="I30" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J30" t="s">
         <v>28</v>
       </c>
       <c r="K30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L30">
         <v>1887</v>
@@ -3450,7 +3450,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C31" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3467,19 +3467,19 @@
         <v>SIMPLE</v>
       </c>
       <c r="G31" t="s">
+        <v>164</v>
+      </c>
+      <c r="H31" t="s">
         <v>165</v>
       </c>
-      <c r="H31" t="s">
-        <v>166</v>
-      </c>
       <c r="I31" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J31" t="s">
         <v>82</v>
       </c>
       <c r="K31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L31">
         <v>1780</v>
@@ -3493,7 +3493,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C32" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3513,16 +3513,16 @@
         <v>80</v>
       </c>
       <c r="H32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J32" t="s">
         <v>71</v>
       </c>
       <c r="K32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L32">
         <v>1750</v>
@@ -3536,7 +3536,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C33" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3556,16 +3556,16 @@
         <v>58</v>
       </c>
       <c r="H33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I33" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="J33" t="s">
         <v>22</v>
       </c>
       <c r="K33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L33">
         <v>2090</v>
@@ -3579,7 +3579,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C34" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3596,19 +3596,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G34" t="s">
+        <v>174</v>
+      </c>
+      <c r="H34" t="s">
         <v>175</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>176</v>
-      </c>
-      <c r="I34" t="s">
-        <v>177</v>
       </c>
       <c r="J34" t="s">
         <v>17</v>
       </c>
       <c r="K34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L34">
         <v>1560</v>
@@ -3622,14 +3622,14 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" t="str">
+        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
+        <v>zona_centre</v>
+      </c>
+      <c r="D35" t="s">
         <v>179</v>
-      </c>
-      <c r="C35" t="str">
-        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
-        <v>zona_centre</v>
-      </c>
-      <c r="D35" t="s">
-        <v>180</v>
       </c>
       <c r="E35" t="s">
         <v>39</v>
@@ -3639,19 +3639,19 @@
         <v>SIMPLE</v>
       </c>
       <c r="G35" t="s">
+        <v>180</v>
+      </c>
+      <c r="H35" t="s">
         <v>181</v>
-      </c>
-      <c r="H35" t="s">
-        <v>182</v>
       </c>
       <c r="I35" t="s">
         <v>34</v>
       </c>
       <c r="J35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L35">
         <v>1900</v>
@@ -3665,7 +3665,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C36" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3682,19 +3682,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H36" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J36" t="s">
         <v>71</v>
       </c>
       <c r="K36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L36">
         <v>1750</v>
@@ -3708,7 +3708,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C37" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3725,19 +3725,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G37" t="s">
+        <v>187</v>
+      </c>
+      <c r="H37" t="s">
         <v>188</v>
       </c>
-      <c r="H37" t="s">
-        <v>189</v>
-      </c>
       <c r="I37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J37" t="s">
         <v>71</v>
       </c>
       <c r="K37" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L37">
         <v>1750</v>
@@ -3751,14 +3751,14 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C38" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_centre</v>
       </c>
       <c r="D38" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E38" t="s">
         <v>25</v>
@@ -3768,19 +3768,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H38" t="s">
+        <v>191</v>
+      </c>
+      <c r="I38" t="s">
+        <v>512</v>
+      </c>
+      <c r="J38" t="s">
+        <v>153</v>
+      </c>
+      <c r="K38" t="s">
         <v>192</v>
-      </c>
-      <c r="I38" t="s">
-        <v>513</v>
-      </c>
-      <c r="J38" t="s">
-        <v>154</v>
-      </c>
-      <c r="K38" t="s">
-        <v>193</v>
       </c>
       <c r="L38">
         <v>1340</v>
@@ -3794,7 +3794,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C39" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3811,19 +3811,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G39" t="s">
+        <v>194</v>
+      </c>
+      <c r="H39" t="s">
         <v>195</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
+        <v>513</v>
+      </c>
+      <c r="J39" t="s">
         <v>196</v>
       </c>
-      <c r="I39" t="s">
-        <v>514</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>197</v>
-      </c>
-      <c r="K39" t="s">
-        <v>198</v>
       </c>
       <c r="L39">
         <v>2138</v>
@@ -3837,7 +3837,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C40" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3854,19 +3854,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G40" t="s">
+        <v>199</v>
+      </c>
+      <c r="H40" t="s">
         <v>200</v>
       </c>
-      <c r="H40" t="s">
+      <c r="I40" t="s">
         <v>201</v>
-      </c>
-      <c r="I40" t="s">
-        <v>202</v>
       </c>
       <c r="J40" t="s">
         <v>17</v>
       </c>
       <c r="K40" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L40">
         <v>1560</v>
@@ -3880,14 +3880,14 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
+        <v>203</v>
+      </c>
+      <c r="C41" t="str">
+        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
+        <v>zona_nord</v>
+      </c>
+      <c r="D41" t="s">
         <v>204</v>
-      </c>
-      <c r="C41" t="str">
-        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
-        <v>zona_nord</v>
-      </c>
-      <c r="D41" t="s">
-        <v>205</v>
       </c>
       <c r="E41" t="s">
         <v>13</v>
@@ -3897,19 +3897,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G41" t="s">
+        <v>205</v>
+      </c>
+      <c r="H41" t="s">
         <v>206</v>
       </c>
-      <c r="H41" t="s">
-        <v>207</v>
-      </c>
       <c r="I41" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J41" t="s">
         <v>82</v>
       </c>
       <c r="K41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L41">
         <v>1780</v>
@@ -3923,7 +3923,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C42" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -3940,19 +3940,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G42" t="s">
+        <v>209</v>
+      </c>
+      <c r="H42" t="s">
         <v>210</v>
       </c>
-      <c r="H42" t="s">
-        <v>211</v>
-      </c>
       <c r="I42" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J42" t="s">
         <v>82</v>
       </c>
       <c r="K42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L42">
         <v>1780</v>
@@ -3966,14 +3966,14 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C43" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D43" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E43" t="s">
         <v>13</v>
@@ -3983,10 +3983,10 @@
         <v>EXIGENT</v>
       </c>
       <c r="G43" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H43" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I43" t="s">
         <v>34</v>
@@ -3995,7 +3995,7 @@
         <v>82</v>
       </c>
       <c r="K43" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L43">
         <v>1780</v>
@@ -4009,14 +4009,14 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C44" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E44" t="s">
         <v>25</v>
@@ -4026,19 +4026,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G44" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H44" t="s">
+        <v>215</v>
+      </c>
+      <c r="I44" t="s">
+        <v>512</v>
+      </c>
+      <c r="J44" t="s">
         <v>216</v>
       </c>
-      <c r="I44" t="s">
-        <v>513</v>
-      </c>
-      <c r="J44" t="s">
-        <v>217</v>
-      </c>
       <c r="K44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L44">
         <v>1854</v>
@@ -4052,14 +4052,14 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C45" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_centre</v>
       </c>
       <c r="D45" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E45" t="s">
         <v>25</v>
@@ -4069,19 +4069,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G45" t="s">
+        <v>218</v>
+      </c>
+      <c r="H45" t="s">
         <v>219</v>
-      </c>
-      <c r="H45" t="s">
-        <v>220</v>
       </c>
       <c r="I45" t="s">
         <v>34</v>
       </c>
       <c r="J45" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K45" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L45">
         <v>1340</v>
@@ -4095,14 +4095,14 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C46" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E46" t="s">
         <v>13</v>
@@ -4112,19 +4112,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G46" t="s">
+        <v>222</v>
+      </c>
+      <c r="H46" t="s">
         <v>223</v>
-      </c>
-      <c r="H46" t="s">
-        <v>224</v>
       </c>
       <c r="I46" t="s">
         <v>34</v>
       </c>
       <c r="J46" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K46" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L46">
         <v>2090</v>
@@ -4138,7 +4138,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C47" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -4155,19 +4155,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G47" t="s">
+        <v>226</v>
+      </c>
+      <c r="H47" t="s">
         <v>227</v>
       </c>
-      <c r="H47" t="s">
-        <v>228</v>
-      </c>
       <c r="I47" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J47" t="s">
         <v>17</v>
       </c>
       <c r="K47" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L47">
         <v>1560</v>
@@ -4181,14 +4181,14 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C48" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E48" t="s">
         <v>13</v>
@@ -4201,16 +4201,16 @@
         <v>80</v>
       </c>
       <c r="H48" t="s">
+        <v>230</v>
+      </c>
+      <c r="I48" t="s">
+        <v>176</v>
+      </c>
+      <c r="J48" t="s">
+        <v>110</v>
+      </c>
+      <c r="K48" t="s">
         <v>231</v>
-      </c>
-      <c r="I48" t="s">
-        <v>177</v>
-      </c>
-      <c r="J48" t="s">
-        <v>111</v>
-      </c>
-      <c r="K48" t="s">
-        <v>232</v>
       </c>
       <c r="L48">
         <v>2090</v>
@@ -4224,7 +4224,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C49" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -4244,16 +4244,16 @@
         <v>68</v>
       </c>
       <c r="H49" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I49" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="J49" t="s">
         <v>49</v>
       </c>
       <c r="K49" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L49">
         <v>2100</v>
@@ -4267,7 +4267,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C50" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -4284,19 +4284,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G50" t="s">
+        <v>236</v>
+      </c>
+      <c r="H50" t="s">
         <v>237</v>
       </c>
-      <c r="H50" t="s">
-        <v>238</v>
-      </c>
       <c r="I50" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J50" t="s">
         <v>28</v>
       </c>
       <c r="K50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L50">
         <v>1887</v>
@@ -4310,7 +4310,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C51" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -4327,19 +4327,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G51" t="s">
+        <v>240</v>
+      </c>
+      <c r="H51" t="s">
         <v>241</v>
       </c>
-      <c r="H51" t="s">
-        <v>242</v>
-      </c>
       <c r="I51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J51" t="s">
         <v>55</v>
       </c>
       <c r="K51" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L51">
         <v>1953</v>
@@ -4353,7 +4353,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C52" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -4370,19 +4370,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G52" t="s">
+        <v>244</v>
+      </c>
+      <c r="H52" t="s">
         <v>245</v>
       </c>
-      <c r="H52" t="s">
-        <v>246</v>
-      </c>
       <c r="I52" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J52" t="s">
         <v>82</v>
       </c>
       <c r="K52" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L52">
         <v>1780</v>
@@ -4396,14 +4396,14 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C53" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E53" t="s">
         <v>13</v>
@@ -4413,19 +4413,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G53" t="s">
+        <v>248</v>
+      </c>
+      <c r="H53" t="s">
         <v>249</v>
       </c>
-      <c r="H53" t="s">
+      <c r="I53" t="s">
+        <v>517</v>
+      </c>
+      <c r="J53" t="s">
+        <v>146</v>
+      </c>
+      <c r="K53" t="s">
         <v>250</v>
-      </c>
-      <c r="I53" t="s">
-        <v>518</v>
-      </c>
-      <c r="J53" t="s">
-        <v>147</v>
-      </c>
-      <c r="K53" t="s">
-        <v>251</v>
       </c>
       <c r="L53">
         <v>1825</v>
@@ -4439,14 +4439,14 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C54" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E54" t="s">
         <v>25</v>
@@ -4456,19 +4456,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G54" t="s">
+        <v>252</v>
+      </c>
+      <c r="H54" t="s">
         <v>253</v>
-      </c>
-      <c r="H54" t="s">
-        <v>254</v>
       </c>
       <c r="I54" t="s">
         <v>34</v>
       </c>
       <c r="J54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K54" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L54">
         <v>1940</v>
@@ -4482,14 +4482,14 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C55" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D55" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E55" t="s">
         <v>13</v>
@@ -4499,19 +4499,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G55" t="s">
+        <v>256</v>
+      </c>
+      <c r="H55" t="s">
         <v>257</v>
       </c>
-      <c r="H55" t="s">
+      <c r="I55" t="s">
+        <v>517</v>
+      </c>
+      <c r="J55" t="s">
+        <v>146</v>
+      </c>
+      <c r="K55" t="s">
         <v>258</v>
-      </c>
-      <c r="I55" t="s">
-        <v>518</v>
-      </c>
-      <c r="J55" t="s">
-        <v>147</v>
-      </c>
-      <c r="K55" t="s">
-        <v>259</v>
       </c>
       <c r="L55">
         <v>1825</v>
@@ -4525,7 +4525,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C56" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -4542,19 +4542,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G56" t="s">
+        <v>260</v>
+      </c>
+      <c r="H56" t="s">
         <v>261</v>
       </c>
-      <c r="H56" t="s">
-        <v>262</v>
-      </c>
       <c r="I56" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J56" t="s">
         <v>71</v>
       </c>
       <c r="K56" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L56">
         <v>1750</v>
@@ -4568,7 +4568,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C57" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -4585,10 +4585,10 @@
         <v>EXIGENT</v>
       </c>
       <c r="G57" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H57" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I57" t="s">
         <v>42</v>
@@ -4597,7 +4597,7 @@
         <v>55</v>
       </c>
       <c r="K57" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L57">
         <v>1953</v>
@@ -4611,7 +4611,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C58" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -4628,10 +4628,10 @@
         <v>EXIGENT</v>
       </c>
       <c r="G58" t="s">
+        <v>267</v>
+      </c>
+      <c r="H58" t="s">
         <v>268</v>
-      </c>
-      <c r="H58" t="s">
-        <v>269</v>
       </c>
       <c r="I58" t="s">
         <v>42</v>
@@ -4640,7 +4640,7 @@
         <v>71</v>
       </c>
       <c r="K58" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L58">
         <v>1750</v>
@@ -4654,7 +4654,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C59" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -4674,16 +4674,16 @@
         <v>32</v>
       </c>
       <c r="H59" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I59" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J59" t="s">
         <v>55</v>
       </c>
       <c r="K59" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L59">
         <v>1953</v>
@@ -4697,14 +4697,14 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C60" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D60" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E60" t="s">
         <v>13</v>
@@ -4714,19 +4714,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G60" t="s">
+        <v>272</v>
+      </c>
+      <c r="H60" t="s">
         <v>273</v>
       </c>
-      <c r="H60" t="s">
+      <c r="I60" t="s">
+        <v>519</v>
+      </c>
+      <c r="J60" t="s">
+        <v>216</v>
+      </c>
+      <c r="K60" t="s">
         <v>274</v>
-      </c>
-      <c r="I60" t="s">
-        <v>520</v>
-      </c>
-      <c r="J60" t="s">
-        <v>217</v>
-      </c>
-      <c r="K60" t="s">
-        <v>275</v>
       </c>
       <c r="L60">
         <v>1854</v>
@@ -4740,14 +4740,14 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C61" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_centre</v>
       </c>
       <c r="D61" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E61" t="s">
         <v>25</v>
@@ -4757,19 +4757,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G61" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H61" t="s">
+        <v>276</v>
+      </c>
+      <c r="I61" t="s">
+        <v>520</v>
+      </c>
+      <c r="J61" t="s">
+        <v>128</v>
+      </c>
+      <c r="K61" t="s">
         <v>277</v>
-      </c>
-      <c r="I61" t="s">
-        <v>521</v>
-      </c>
-      <c r="J61" t="s">
-        <v>129</v>
-      </c>
-      <c r="K61" t="s">
-        <v>278</v>
       </c>
       <c r="L61">
         <v>1232</v>
@@ -4783,7 +4783,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C62" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -4800,19 +4800,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G62" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H62" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I62" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J62" t="s">
         <v>49</v>
       </c>
       <c r="K62" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L62">
         <v>2100</v>
@@ -4826,14 +4826,14 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C63" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D63" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E63" t="s">
         <v>13</v>
@@ -4843,19 +4843,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G63" t="s">
+        <v>282</v>
+      </c>
+      <c r="H63" t="s">
         <v>283</v>
       </c>
-      <c r="H63" t="s">
+      <c r="I63" t="s">
+        <v>522</v>
+      </c>
+      <c r="J63" t="s">
+        <v>146</v>
+      </c>
+      <c r="K63" t="s">
         <v>284</v>
-      </c>
-      <c r="I63" t="s">
-        <v>523</v>
-      </c>
-      <c r="J63" t="s">
-        <v>147</v>
-      </c>
-      <c r="K63" t="s">
-        <v>285</v>
       </c>
       <c r="L63">
         <v>1825</v>
@@ -4869,7 +4869,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C64" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -4886,19 +4886,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G64" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H64" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J64" t="s">
         <v>55</v>
       </c>
       <c r="K64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L64">
         <v>1953</v>
@@ -4912,7 +4912,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C65" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -4929,10 +4929,10 @@
         <v>EXIGENT</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I65" t="s">
         <v>42</v>
@@ -4941,7 +4941,7 @@
         <v>55</v>
       </c>
       <c r="K65" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L65">
         <v>1953</v>
@@ -4955,7 +4955,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C66" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -4972,19 +4972,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G66" t="s">
+        <v>291</v>
+      </c>
+      <c r="H66" t="s">
         <v>292</v>
       </c>
-      <c r="H66" t="s">
-        <v>293</v>
-      </c>
       <c r="I66" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J66" t="s">
         <v>82</v>
       </c>
       <c r="K66" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L66">
         <v>1780</v>
@@ -4998,14 +4998,14 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C67" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D67" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E67" t="s">
         <v>13</v>
@@ -5015,19 +5015,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G67" t="s">
+        <v>295</v>
+      </c>
+      <c r="H67" t="s">
+        <v>121</v>
+      </c>
+      <c r="I67" t="s">
+        <v>517</v>
+      </c>
+      <c r="J67" t="s">
+        <v>146</v>
+      </c>
+      <c r="K67" t="s">
         <v>296</v>
-      </c>
-      <c r="H67" t="s">
-        <v>122</v>
-      </c>
-      <c r="I67" t="s">
-        <v>518</v>
-      </c>
-      <c r="J67" t="s">
-        <v>147</v>
-      </c>
-      <c r="K67" t="s">
-        <v>297</v>
       </c>
       <c r="L67">
         <v>1825</v>
@@ -5041,7 +5041,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C68" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5061,16 +5061,16 @@
         <v>14</v>
       </c>
       <c r="H68" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I68" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="J68" t="s">
         <v>71</v>
       </c>
       <c r="K68" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L68">
         <v>1750</v>
@@ -5084,7 +5084,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C69" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5101,19 +5101,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H69" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I69" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J69" t="s">
         <v>71</v>
       </c>
       <c r="K69" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L69">
         <v>1750</v>
@@ -5127,7 +5127,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C70" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5144,19 +5144,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G70" t="s">
+        <v>304</v>
+      </c>
+      <c r="H70" t="s">
         <v>305</v>
       </c>
-      <c r="H70" t="s">
-        <v>306</v>
-      </c>
       <c r="I70" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J70" t="s">
         <v>71</v>
       </c>
       <c r="K70" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L70">
         <v>1750</v>
@@ -5170,14 +5170,14 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C71" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D71" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E71" t="s">
         <v>13</v>
@@ -5190,16 +5190,16 @@
         <v>63</v>
       </c>
       <c r="H71" t="s">
+        <v>308</v>
+      </c>
+      <c r="I71" t="s">
+        <v>525</v>
+      </c>
+      <c r="J71" t="s">
+        <v>216</v>
+      </c>
+      <c r="K71" t="s">
         <v>309</v>
-      </c>
-      <c r="I71" t="s">
-        <v>526</v>
-      </c>
-      <c r="J71" t="s">
-        <v>217</v>
-      </c>
-      <c r="K71" t="s">
-        <v>310</v>
       </c>
       <c r="L71">
         <v>1854</v>
@@ -5213,7 +5213,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C72" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5230,19 +5230,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G72" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H72" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I72" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J72" t="s">
         <v>17</v>
       </c>
       <c r="K72" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L72">
         <v>1560</v>
@@ -5256,7 +5256,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C73" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5273,10 +5273,10 @@
         <v>EXIGENT</v>
       </c>
       <c r="G73" t="s">
+        <v>314</v>
+      </c>
+      <c r="H73" t="s">
         <v>315</v>
-      </c>
-      <c r="H73" t="s">
-        <v>316</v>
       </c>
       <c r="I73" t="s">
         <v>42</v>
@@ -5285,7 +5285,7 @@
         <v>71</v>
       </c>
       <c r="K73" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L73">
         <v>1750</v>
@@ -5299,7 +5299,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C74" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5316,19 +5316,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G74" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H74" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I74" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J74" t="s">
         <v>17</v>
       </c>
       <c r="K74" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L74">
         <v>1560</v>
@@ -5342,7 +5342,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C75" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5362,7 +5362,7 @@
         <v>20</v>
       </c>
       <c r="H75" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I75" t="s">
         <v>42</v>
@@ -5371,7 +5371,7 @@
         <v>55</v>
       </c>
       <c r="K75" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L75">
         <v>1953</v>
@@ -5385,7 +5385,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C76" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5405,16 +5405,16 @@
         <v>32</v>
       </c>
       <c r="H76" t="s">
+        <v>324</v>
+      </c>
+      <c r="I76" t="s">
         <v>325</v>
-      </c>
-      <c r="I76" t="s">
-        <v>326</v>
       </c>
       <c r="J76" t="s">
         <v>49</v>
       </c>
       <c r="K76" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L76">
         <v>2100</v>
@@ -5428,14 +5428,14 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C77" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_centre</v>
       </c>
       <c r="D77" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E77" t="s">
         <v>25</v>
@@ -5445,19 +5445,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G77" t="s">
+        <v>328</v>
+      </c>
+      <c r="H77" t="s">
         <v>329</v>
       </c>
-      <c r="H77" t="s">
+      <c r="I77" t="s">
+        <v>527</v>
+      </c>
+      <c r="J77" t="s">
+        <v>128</v>
+      </c>
+      <c r="K77" t="s">
         <v>330</v>
-      </c>
-      <c r="I77" t="s">
-        <v>528</v>
-      </c>
-      <c r="J77" t="s">
-        <v>129</v>
-      </c>
-      <c r="K77" t="s">
-        <v>331</v>
       </c>
       <c r="L77">
         <v>1232</v>
@@ -5471,7 +5471,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C78" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5488,19 +5488,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G78" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H78" t="s">
+        <v>332</v>
+      </c>
+      <c r="I78" t="s">
         <v>333</v>
-      </c>
-      <c r="I78" t="s">
-        <v>334</v>
       </c>
       <c r="J78" t="s">
         <v>71</v>
       </c>
       <c r="K78" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L78">
         <v>1750</v>
@@ -5514,7 +5514,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C79" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5531,10 +5531,10 @@
         <v>COMPLEX</v>
       </c>
       <c r="G79" t="s">
+        <v>336</v>
+      </c>
+      <c r="H79" t="s">
         <v>337</v>
-      </c>
-      <c r="H79" t="s">
-        <v>338</v>
       </c>
       <c r="I79" t="s">
         <v>42</v>
@@ -5543,7 +5543,7 @@
         <v>43</v>
       </c>
       <c r="K79" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L79">
         <v>1940</v>
@@ -5557,7 +5557,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C80" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5574,19 +5574,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G80" t="s">
+        <v>340</v>
+      </c>
+      <c r="H80" t="s">
         <v>341</v>
       </c>
-      <c r="H80" t="s">
-        <v>342</v>
-      </c>
       <c r="I80" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="J80" t="s">
         <v>17</v>
       </c>
       <c r="K80" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L80">
         <v>1560</v>
@@ -5600,14 +5600,14 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
+        <v>343</v>
+      </c>
+      <c r="C81" t="str">
+        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
+        <v>zona_sud</v>
+      </c>
+      <c r="D81" t="s">
         <v>344</v>
-      </c>
-      <c r="C81" t="str">
-        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
-        <v>zona_sud</v>
-      </c>
-      <c r="D81" t="s">
-        <v>345</v>
       </c>
       <c r="E81" t="s">
         <v>13</v>
@@ -5617,19 +5617,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G81" t="s">
+        <v>345</v>
+      </c>
+      <c r="H81" t="s">
         <v>346</v>
-      </c>
-      <c r="H81" t="s">
-        <v>347</v>
       </c>
       <c r="I81" t="s">
         <v>42</v>
       </c>
       <c r="J81" t="s">
+        <v>347</v>
+      </c>
+      <c r="K81" t="s">
         <v>348</v>
-      </c>
-      <c r="K81" t="s">
-        <v>349</v>
       </c>
       <c r="L81">
         <v>1945</v>
@@ -5643,7 +5643,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C82" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5660,19 +5660,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G82" t="s">
+        <v>350</v>
+      </c>
+      <c r="H82" t="s">
         <v>351</v>
       </c>
-      <c r="H82" t="s">
-        <v>352</v>
-      </c>
       <c r="I82" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J82" t="s">
         <v>71</v>
       </c>
       <c r="K82" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L82">
         <v>1750</v>
@@ -5686,7 +5686,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C83" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5703,19 +5703,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G83" t="s">
+        <v>354</v>
+      </c>
+      <c r="H83" t="s">
         <v>355</v>
       </c>
-      <c r="H83" t="s">
+      <c r="I83" t="s">
         <v>356</v>
-      </c>
-      <c r="I83" t="s">
-        <v>357</v>
       </c>
       <c r="J83" t="s">
         <v>17</v>
       </c>
       <c r="K83" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L83">
         <v>1560</v>
@@ -5729,7 +5729,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C84" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5749,7 +5749,7 @@
         <v>58</v>
       </c>
       <c r="H84" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I84" t="s">
         <v>34</v>
@@ -5758,7 +5758,7 @@
         <v>49</v>
       </c>
       <c r="K84" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L84">
         <v>2100</v>
@@ -5772,7 +5772,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C85" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5789,19 +5789,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G85" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H85" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I85" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J85" t="s">
         <v>71</v>
       </c>
       <c r="K85" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="L85">
         <v>1750</v>
@@ -5815,14 +5815,14 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C86" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D86" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E86" t="s">
         <v>13</v>
@@ -5832,19 +5832,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G86" t="s">
+        <v>364</v>
+      </c>
+      <c r="H86" t="s">
         <v>365</v>
       </c>
-      <c r="H86" t="s">
+      <c r="I86" t="s">
+        <v>522</v>
+      </c>
+      <c r="J86" t="s">
+        <v>146</v>
+      </c>
+      <c r="K86" t="s">
         <v>366</v>
-      </c>
-      <c r="I86" t="s">
-        <v>523</v>
-      </c>
-      <c r="J86" t="s">
-        <v>147</v>
-      </c>
-      <c r="K86" t="s">
-        <v>367</v>
       </c>
       <c r="L86">
         <v>1825</v>
@@ -5858,14 +5858,14 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
+        <v>367</v>
+      </c>
+      <c r="C87" t="str">
+        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
+        <v>zona_nord</v>
+      </c>
+      <c r="D87" t="s">
         <v>368</v>
-      </c>
-      <c r="C87" t="str">
-        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
-        <v>zona_nord</v>
-      </c>
-      <c r="D87" t="s">
-        <v>369</v>
       </c>
       <c r="E87" t="s">
         <v>39</v>
@@ -5875,19 +5875,19 @@
         <v>SIMPLE</v>
       </c>
       <c r="G87" t="s">
+        <v>369</v>
+      </c>
+      <c r="H87" t="s">
         <v>370</v>
       </c>
-      <c r="H87" t="s">
+      <c r="I87" t="s">
+        <v>529</v>
+      </c>
+      <c r="J87" t="s">
         <v>371</v>
       </c>
-      <c r="I87" t="s">
-        <v>530</v>
-      </c>
-      <c r="J87" t="s">
+      <c r="K87" t="s">
         <v>372</v>
-      </c>
-      <c r="K87" t="s">
-        <v>373</v>
       </c>
       <c r="L87">
         <v>2408</v>
@@ -5901,7 +5901,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C88" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -5918,19 +5918,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G88" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H88" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I88" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J88" t="s">
         <v>17</v>
       </c>
       <c r="K88" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L88">
         <v>1560</v>
@@ -5944,14 +5944,14 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C89" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D89" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E89" t="s">
         <v>13</v>
@@ -5964,16 +5964,16 @@
         <v>74</v>
       </c>
       <c r="H89" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I89" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J89" t="s">
         <v>82</v>
       </c>
       <c r="K89" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L89">
         <v>1780</v>
@@ -5987,7 +5987,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C90" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6004,19 +6004,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G90" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H90" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I90" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="J90" t="s">
         <v>82</v>
       </c>
       <c r="K90" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L90">
         <v>1780</v>
@@ -6030,14 +6030,14 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C91" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D91" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E91" t="s">
         <v>25</v>
@@ -6047,19 +6047,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G91" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H91" t="s">
+        <v>383</v>
+      </c>
+      <c r="I91" t="s">
+        <v>517</v>
+      </c>
+      <c r="J91" t="s">
+        <v>133</v>
+      </c>
+      <c r="K91" t="s">
         <v>384</v>
-      </c>
-      <c r="I91" t="s">
-        <v>518</v>
-      </c>
-      <c r="J91" t="s">
-        <v>134</v>
-      </c>
-      <c r="K91" t="s">
-        <v>385</v>
       </c>
       <c r="L91">
         <v>1920</v>
@@ -6073,14 +6073,14 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C92" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_centre</v>
       </c>
       <c r="D92" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E92" t="s">
         <v>25</v>
@@ -6090,19 +6090,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G92" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H92" t="s">
+        <v>386</v>
+      </c>
+      <c r="I92" t="s">
+        <v>532</v>
+      </c>
+      <c r="J92" t="s">
         <v>387</v>
       </c>
-      <c r="I92" t="s">
-        <v>533</v>
-      </c>
-      <c r="J92" t="s">
+      <c r="K92" t="s">
         <v>388</v>
-      </c>
-      <c r="K92" t="s">
-        <v>389</v>
       </c>
       <c r="L92">
         <v>2090</v>
@@ -6116,7 +6116,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C93" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6133,10 +6133,10 @@
         <v>EXIGENT</v>
       </c>
       <c r="G93" t="s">
+        <v>390</v>
+      </c>
+      <c r="H93" t="s">
         <v>391</v>
-      </c>
-      <c r="H93" t="s">
-        <v>392</v>
       </c>
       <c r="I93" t="s">
         <v>16</v>
@@ -6145,7 +6145,7 @@
         <v>49</v>
       </c>
       <c r="K93" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L93">
         <v>2100</v>
@@ -6159,14 +6159,14 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
+        <v>393</v>
+      </c>
+      <c r="C94" t="str">
+        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
+        <v>zona_sud</v>
+      </c>
+      <c r="D94" t="s">
         <v>394</v>
-      </c>
-      <c r="C94" t="str">
-        <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
-        <v>zona_sud</v>
-      </c>
-      <c r="D94" t="s">
-        <v>395</v>
       </c>
       <c r="E94" t="s">
         <v>39</v>
@@ -6176,19 +6176,19 @@
         <v>SIMPLE</v>
       </c>
       <c r="G94" t="s">
+        <v>395</v>
+      </c>
+      <c r="H94" t="s">
         <v>396</v>
       </c>
-      <c r="H94" t="s">
+      <c r="I94" t="s">
+        <v>85</v>
+      </c>
+      <c r="J94" t="s">
         <v>397</v>
       </c>
-      <c r="I94" t="s">
-        <v>86</v>
-      </c>
-      <c r="J94" t="s">
+      <c r="K94" t="s">
         <v>398</v>
-      </c>
-      <c r="K94" t="s">
-        <v>399</v>
       </c>
       <c r="L94">
         <v>2040</v>
@@ -6202,14 +6202,14 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C95" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D95" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E95" t="s">
         <v>13</v>
@@ -6219,19 +6219,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G95" t="s">
+        <v>400</v>
+      </c>
+      <c r="H95" t="s">
         <v>401</v>
       </c>
-      <c r="H95" t="s">
+      <c r="I95" t="s">
+        <v>176</v>
+      </c>
+      <c r="J95" t="s">
+        <v>133</v>
+      </c>
+      <c r="K95" t="s">
         <v>402</v>
-      </c>
-      <c r="I95" t="s">
-        <v>177</v>
-      </c>
-      <c r="J95" t="s">
-        <v>134</v>
-      </c>
-      <c r="K95" t="s">
-        <v>403</v>
       </c>
       <c r="L95">
         <v>1920</v>
@@ -6245,14 +6245,14 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C96" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_centre</v>
       </c>
       <c r="D96" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E96" t="s">
         <v>39</v>
@@ -6262,19 +6262,19 @@
         <v>SIMPLE</v>
       </c>
       <c r="G96" t="s">
+        <v>404</v>
+      </c>
+      <c r="H96" t="s">
         <v>405</v>
-      </c>
-      <c r="H96" t="s">
-        <v>406</v>
       </c>
       <c r="I96" t="s">
         <v>34</v>
       </c>
       <c r="J96" t="s">
+        <v>406</v>
+      </c>
+      <c r="K96" t="s">
         <v>407</v>
-      </c>
-      <c r="K96" t="s">
-        <v>408</v>
       </c>
       <c r="L96">
         <v>1780</v>
@@ -6288,7 +6288,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C97" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6305,19 +6305,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G97" t="s">
+        <v>409</v>
+      </c>
+      <c r="H97" t="s">
         <v>410</v>
       </c>
-      <c r="H97" t="s">
-        <v>411</v>
-      </c>
       <c r="I97" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J97" t="s">
         <v>71</v>
       </c>
       <c r="K97" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L97">
         <v>1750</v>
@@ -6331,14 +6331,14 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C98" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D98" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E98" t="s">
         <v>13</v>
@@ -6348,19 +6348,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G98" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H98" t="s">
+        <v>413</v>
+      </c>
+      <c r="I98" t="s">
+        <v>511</v>
+      </c>
+      <c r="J98" t="s">
+        <v>104</v>
+      </c>
+      <c r="K98" t="s">
         <v>414</v>
-      </c>
-      <c r="I98" t="s">
-        <v>512</v>
-      </c>
-      <c r="J98" t="s">
-        <v>105</v>
-      </c>
-      <c r="K98" t="s">
-        <v>415</v>
       </c>
       <c r="L98">
         <v>1940</v>
@@ -6374,14 +6374,14 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C99" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D99" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E99" t="s">
         <v>13</v>
@@ -6391,19 +6391,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G99" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H99" t="s">
+        <v>416</v>
+      </c>
+      <c r="I99" t="s">
+        <v>525</v>
+      </c>
+      <c r="J99" t="s">
+        <v>216</v>
+      </c>
+      <c r="K99" t="s">
         <v>417</v>
-      </c>
-      <c r="I99" t="s">
-        <v>526</v>
-      </c>
-      <c r="J99" t="s">
-        <v>217</v>
-      </c>
-      <c r="K99" t="s">
-        <v>418</v>
       </c>
       <c r="L99">
         <v>1854</v>
@@ -6417,14 +6417,14 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C100" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D100" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E100" t="s">
         <v>25</v>
@@ -6434,19 +6434,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G100" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H100" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I100" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J100" t="s">
         <v>82</v>
       </c>
       <c r="K100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L100">
         <v>1780</v>
@@ -6460,7 +6460,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C101" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6480,16 +6480,16 @@
         <v>68</v>
       </c>
       <c r="H101" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I101" t="s">
+        <v>422</v>
+      </c>
+      <c r="J101" t="s">
         <v>423</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>424</v>
-      </c>
-      <c r="K101" t="s">
-        <v>425</v>
       </c>
       <c r="L101">
         <v>1550</v>
@@ -6503,7 +6503,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C102" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6520,19 +6520,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G102" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H102" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I102" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J102" t="s">
         <v>55</v>
       </c>
       <c r="K102" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L102">
         <v>1953</v>
@@ -6546,7 +6546,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C103" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6563,19 +6563,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G103" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H103" t="s">
+        <v>429</v>
+      </c>
+      <c r="I103" t="s">
         <v>430</v>
-      </c>
-      <c r="I103" t="s">
-        <v>431</v>
       </c>
       <c r="J103" t="s">
         <v>17</v>
       </c>
       <c r="K103" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L103">
         <v>1560</v>
@@ -6589,7 +6589,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C104" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6606,19 +6606,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G104" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H104" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I104" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J104" t="s">
         <v>17</v>
       </c>
       <c r="K104" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L104">
         <v>1560</v>
@@ -6632,7 +6632,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C105" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6649,19 +6649,19 @@
         <v>SIMPLE</v>
       </c>
       <c r="G105" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H105" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J105" t="s">
         <v>28</v>
       </c>
       <c r="K105" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L105">
         <v>1887</v>
@@ -6675,7 +6675,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C106" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6695,16 +6695,16 @@
         <v>32</v>
       </c>
       <c r="H106" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I106" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J106" t="s">
         <v>71</v>
       </c>
       <c r="K106" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L106">
         <v>1750</v>
@@ -6718,7 +6718,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C107" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6738,7 +6738,7 @@
         <v>68</v>
       </c>
       <c r="H107" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I107" t="s">
         <v>42</v>
@@ -6747,7 +6747,7 @@
         <v>43</v>
       </c>
       <c r="K107" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L107">
         <v>1940</v>
@@ -6761,7 +6761,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C108" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6778,19 +6778,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G108" t="s">
+        <v>443</v>
+      </c>
+      <c r="H108" t="s">
         <v>444</v>
       </c>
-      <c r="H108" t="s">
-        <v>445</v>
-      </c>
       <c r="I108" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J108" t="s">
         <v>55</v>
       </c>
       <c r="K108" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L108">
         <v>1953</v>
@@ -6804,14 +6804,14 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C109" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_centre</v>
       </c>
       <c r="D109" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E109" t="s">
         <v>25</v>
@@ -6821,19 +6821,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G109" t="s">
+        <v>447</v>
+      </c>
+      <c r="H109" t="s">
         <v>448</v>
       </c>
-      <c r="H109" t="s">
+      <c r="I109" t="s">
+        <v>519</v>
+      </c>
+      <c r="J109" t="s">
+        <v>128</v>
+      </c>
+      <c r="K109" t="s">
         <v>449</v>
-      </c>
-      <c r="I109" t="s">
-        <v>520</v>
-      </c>
-      <c r="J109" t="s">
-        <v>129</v>
-      </c>
-      <c r="K109" t="s">
-        <v>450</v>
       </c>
       <c r="L109">
         <v>1232</v>
@@ -6847,7 +6847,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C110" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6864,19 +6864,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G110" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H110" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I110" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J110" t="s">
         <v>71</v>
       </c>
       <c r="K110" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L110">
         <v>1750</v>
@@ -6890,7 +6890,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C111" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6907,19 +6907,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G111" t="s">
+        <v>454</v>
+      </c>
+      <c r="H111" t="s">
         <v>455</v>
       </c>
-      <c r="H111" t="s">
-        <v>456</v>
-      </c>
       <c r="I111" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J111" t="s">
         <v>49</v>
       </c>
       <c r="K111" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L111">
         <v>2100</v>
@@ -6933,14 +6933,14 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C112" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D112" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E112" t="s">
         <v>13</v>
@@ -6953,16 +6953,16 @@
         <v>58</v>
       </c>
       <c r="H112" t="s">
+        <v>458</v>
+      </c>
+      <c r="I112" t="s">
+        <v>517</v>
+      </c>
+      <c r="J112" t="s">
+        <v>146</v>
+      </c>
+      <c r="K112" t="s">
         <v>459</v>
-      </c>
-      <c r="I112" t="s">
-        <v>518</v>
-      </c>
-      <c r="J112" t="s">
-        <v>147</v>
-      </c>
-      <c r="K112" t="s">
-        <v>460</v>
       </c>
       <c r="L112">
         <v>1825</v>
@@ -6976,7 +6976,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C113" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -6993,19 +6993,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G113" t="s">
+        <v>461</v>
+      </c>
+      <c r="H113" t="s">
         <v>462</v>
       </c>
-      <c r="H113" t="s">
-        <v>463</v>
-      </c>
       <c r="I113" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J113" t="s">
         <v>49</v>
       </c>
       <c r="K113" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L113">
         <v>2100</v>
@@ -7019,7 +7019,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C114" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -7039,16 +7039,16 @@
         <v>47</v>
       </c>
       <c r="H114" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I114" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="J114" t="s">
         <v>17</v>
       </c>
       <c r="K114" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L114">
         <v>1560</v>
@@ -7062,7 +7062,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C115" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -7079,19 +7079,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G115" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H115" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I115" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J115" t="s">
         <v>17</v>
       </c>
       <c r="K115" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L115">
         <v>1560</v>
@@ -7105,7 +7105,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C116" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -7122,19 +7122,19 @@
         <v>SIMPLE</v>
       </c>
       <c r="G116" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H116" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I116" t="s">
         <v>34</v>
       </c>
       <c r="J116" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K116" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L116">
         <v>1618</v>
@@ -7148,7 +7148,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C117" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
@@ -7165,19 +7165,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G117" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H117" t="s">
+        <v>473</v>
+      </c>
+      <c r="I117" t="s">
         <v>474</v>
-      </c>
-      <c r="I117" t="s">
-        <v>475</v>
       </c>
       <c r="J117" t="s">
         <v>17</v>
       </c>
       <c r="K117" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L117">
         <v>1560</v>
@@ -7191,14 +7191,14 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C118" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_centre</v>
       </c>
       <c r="D118" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E118" t="s">
         <v>39</v>
@@ -7211,16 +7211,16 @@
         <v>40</v>
       </c>
       <c r="H118" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I118" t="s">
         <v>34</v>
       </c>
       <c r="J118" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K118" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L118">
         <v>1900</v>
@@ -7234,14 +7234,14 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C119" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_sud</v>
       </c>
       <c r="D119" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E119" t="s">
         <v>13</v>
@@ -7251,19 +7251,19 @@
         <v>EXIGENT</v>
       </c>
       <c r="G119" t="s">
+        <v>480</v>
+      </c>
+      <c r="H119" t="s">
         <v>481</v>
       </c>
-      <c r="H119" t="s">
+      <c r="I119" t="s">
+        <v>536</v>
+      </c>
+      <c r="J119" t="s">
+        <v>397</v>
+      </c>
+      <c r="K119" t="s">
         <v>482</v>
-      </c>
-      <c r="I119" t="s">
-        <v>537</v>
-      </c>
-      <c r="J119" t="s">
-        <v>398</v>
-      </c>
-      <c r="K119" t="s">
-        <v>483</v>
       </c>
       <c r="L119">
         <v>2040</v>
@@ -7277,14 +7277,14 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C120" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D120" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
@@ -7294,19 +7294,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G120" t="s">
+        <v>484</v>
+      </c>
+      <c r="H120" t="s">
         <v>485</v>
       </c>
-      <c r="H120" t="s">
-        <v>486</v>
-      </c>
       <c r="I120" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J120" t="s">
         <v>82</v>
       </c>
       <c r="K120" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L120">
         <v>1780</v>
@@ -7320,14 +7320,14 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C121" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E121" t="s">
         <v>25</v>
@@ -7337,16 +7337,16 @@
         <v>COMPLEX</v>
       </c>
       <c r="G121" t="s">
+        <v>487</v>
+      </c>
+      <c r="H121" t="s">
         <v>488</v>
       </c>
-      <c r="H121" t="s">
+      <c r="I121" t="s">
+        <v>333</v>
+      </c>
+      <c r="J121" t="s">
         <v>489</v>
-      </c>
-      <c r="I121" t="s">
-        <v>334</v>
-      </c>
-      <c r="J121" t="s">
-        <v>490</v>
       </c>
       <c r="K121" t="s">
         <v>71</v>
@@ -7363,14 +7363,14 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C122" t="str">
         <f>VLOOKUP(routes[[#This Row],[zone]],Hoja2!A$1:B$20,2,FALSE)</f>
         <v>zona_nord</v>
       </c>
       <c r="D122" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E122" t="s">
         <v>25</v>
@@ -7380,19 +7380,19 @@
         <v>COMPLEX</v>
       </c>
       <c r="G122" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H122" t="s">
+        <v>491</v>
+      </c>
+      <c r="I122" t="s">
+        <v>519</v>
+      </c>
+      <c r="J122" t="s">
         <v>492</v>
       </c>
-      <c r="I122" t="s">
-        <v>520</v>
-      </c>
-      <c r="J122" t="s">
+      <c r="K122" t="s">
         <v>493</v>
-      </c>
-      <c r="K122" t="s">
-        <v>494</v>
       </c>
       <c r="L122">
         <v>1830</v>
@@ -7423,7 +7423,7 @@
         <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>39</v>
@@ -7437,13 +7437,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -7451,7 +7451,7 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>25</v>
@@ -7465,7 +7465,7 @@
         <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -7473,7 +7473,7 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -7481,7 +7481,7 @@
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -7489,7 +7489,7 @@
         <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -7497,7 +7497,7 @@
         <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -7505,39 +7505,39 @@
         <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B12" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -7545,55 +7545,55 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B18" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B19" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B20" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/data/routes_corretgides.xlsx
+++ b/data/routes_corretgides.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{91DA7092-20EF-3849-ACEC-7806277071BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDBF4CF9-95B0-4743-BC36-2FD7AC385F91}"/>
   <bookViews>
-    <workbookView xWindow="17540" yWindow="7660" windowWidth="40380" windowHeight="17440" xr2:uid="{DACA9C36-F0F5-EC4B-9BA5-459550E34FB7}"/>
+    <workbookView xWindow="17520" yWindow="7640" windowWidth="40380" windowHeight="17440" xr2:uid="{DACA9C36-F0F5-EC4B-9BA5-459550E34FB7}"/>
   </bookViews>
   <sheets>
     <sheet name="routes" sheetId="2" r:id="rId1"/>
@@ -1773,6 +1773,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
